--- a/out/MLP-mamba2_repeat_4_000008.xlsx
+++ b/out/MLP-mamba2_repeat_4_000008.xlsx
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.602580650042519</v>
+        <v>1.157166170459627</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>1.204705233669806</v>
+        <v>1.157166170459627</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>1.804705233669806</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>-1.002580650042519</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-1.602580650042519</v>
+        <v>-1.045076465039656</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-1.602580650042519</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>1</v>
       </c>
       <c r="JB8" t="n">
-        <v>1.204705233669806</v>
+        <v>1.157166170459627</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-1.602580650042519</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB10" t="n">
-        <v>-1.602580650042519</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-1.602580650042519</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>1</v>
       </c>
       <c r="JB12" t="n">
-        <v>1.204705233669806</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.002580650042519</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>1</v>
       </c>
       <c r="JB14" t="n">
-        <v>1.804705233669806</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-1.002580650042519</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>1</v>
       </c>
       <c r="JB16" t="n">
-        <v>1.804705233669806</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-1.602580650042519</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-1.002580650042519</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-1.602580650042519</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-1.602580650042519</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB21" t="n">
-        <v>-1.602580650042519</v>
+        <v>1.157166170459627</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-1.602580650042519</v>
+        <v>-1.045076465039656</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>1</v>
       </c>
       <c r="JB23" t="n">
-        <v>1.804705233669806</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-1.002580650042519</v>
+        <v>-1.045076465039656</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>1.804705233669806</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-1.002580650042519</v>
+        <v>-1.045076465039656</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB27" t="n">
-        <v>-1.002580650042519</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-1.602580650042519</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>-1.602580650042519</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>1</v>
       </c>
       <c r="JB30" t="n">
-        <v>1.804705233669806</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>1.804705233669806</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>1</v>
       </c>
       <c r="JB32" t="n">
-        <v>1.804705233669806</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-1.002580650042519</v>
+        <v>-1.045076465039656</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>1</v>
       </c>
       <c r="JB34" t="n">
-        <v>1.804705233669806</v>
+        <v>1.157166170459627</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>1.804705233669806</v>
+        <v>1.157166170459627</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-1.002580650042519</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>1.804705233669806</v>
+        <v>1.157166170459627</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>-1.602580650042519</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-1.602580650042519</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>1.204705233669806</v>
+        <v>1.157166170459627</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>1.804705233669806</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>1.804705233669806</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.804705233669806</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,7 +35924,7 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.804705233669806</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36719,10 +36719,10 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>1.804705233669806</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC45" t="n">
-        <v>-0.0001411644149408676</v>
+        <v>-0.0001400802099283319</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.1621707996420336</v>
+        <v>-0.1609252563232461</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-1.602580650042519</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC46" t="n">
-        <v>-0.1623119640569745</v>
+        <v>-0.1610653365331744</v>
       </c>
     </row>
     <row r="47">
@@ -38309,10 +38309,10 @@
         <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>1.204705233669806</v>
+        <v>1.157166170459627</v>
       </c>
       <c r="JC47" t="n">
-        <v>-0.1623119640569745</v>
+        <v>-0.1610653365331744</v>
       </c>
     </row>
     <row r="48">
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-1.602580650042519</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC48" t="n">
-        <v>-0.1623119640569745</v>
+        <v>-0.1610653365331744</v>
       </c>
     </row>
     <row r="49">
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-1.602580650042519</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC49" t="n">
-        <v>-0.1623119640569745</v>
+        <v>-0.1610653365331744</v>
       </c>
     </row>
     <row r="50">
@@ -40694,10 +40694,10 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-1.602580650042519</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC50" t="n">
-        <v>-0.1623119640569745</v>
+        <v>-0.1610653365331744</v>
       </c>
     </row>
     <row r="51">
@@ -41489,10 +41489,10 @@
         <v>1</v>
       </c>
       <c r="JB51" t="n">
-        <v>1.204705233669806</v>
+        <v>1.157166170459627</v>
       </c>
       <c r="JC51" t="n">
-        <v>-0.1623119640569745</v>
+        <v>-0.1610653365331744</v>
       </c>
     </row>
     <row r="52">
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.602580650042519</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC52" t="n">
-        <v>-0.1623119640569745</v>
+        <v>-0.1610653365331744</v>
       </c>
     </row>
     <row r="53">
@@ -43079,10 +43079,10 @@
         <v>1</v>
       </c>
       <c r="JB53" t="n">
-        <v>1.804705233669806</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC53" t="n">
-        <v>-0.1623119640569745</v>
+        <v>-0.1610653365331744</v>
       </c>
     </row>
     <row r="54">
@@ -43874,10 +43874,10 @@
         <v>1</v>
       </c>
       <c r="JB54" t="n">
-        <v>1.804705233669806</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC54" t="n">
-        <v>-0.1623119640569745</v>
+        <v>-0.1610653365331744</v>
       </c>
     </row>
     <row r="55">
@@ -44669,10 +44669,10 @@
         <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>1.804705233669806</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC55" t="n">
-        <v>-0.1623119640569745</v>
+        <v>-0.1610653365331744</v>
       </c>
     </row>
     <row r="56">
@@ -45464,10 +45464,10 @@
         <v>1</v>
       </c>
       <c r="JB56" t="n">
-        <v>1.804705233669806</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC56" t="n">
-        <v>-0.1623119640569745</v>
+        <v>-0.1610653365331744</v>
       </c>
     </row>
     <row r="57">
@@ -46259,10 +46259,10 @@
         <v>1</v>
       </c>
       <c r="JB57" t="n">
-        <v>1.804705233669806</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC57" t="n">
-        <v>-0.1623119640569745</v>
+        <v>-0.1610653365331744</v>
       </c>
     </row>
     <row r="58">
@@ -47054,10 +47054,10 @@
         <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>1.804705233669806</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC58" t="n">
-        <v>-0.1623119640569745</v>
+        <v>-0.1610653365331744</v>
       </c>
     </row>
     <row r="59">
@@ -47849,10 +47849,10 @@
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>1.804705233669806</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC59" t="n">
-        <v>-0.1624338673807879</v>
+        <v>-0.1611864152315984</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.438336590095572</v>
+        <v>0.4353711682502186</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-1.602580650042519</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.7150809351146759</v>
+        <v>0.7103923643335108</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.03123135342668109</v>
+        <v>0.03102010432907314</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>1</v>
       </c>
       <c r="JB61" t="n">
-        <v>1.204705233669806</v>
+        <v>1.157166170459627</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.3385039852042352</v>
+        <v>0.3363625806186774</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.05476915272888735</v>
+        <v>0.05439882210839907</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>1</v>
       </c>
       <c r="JB62" t="n">
-        <v>1.204705233669806</v>
+        <v>1.157166170459627</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.416800698349921</v>
+        <v>0.4141296951803143</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.06653836416652441</v>
+        <v>0.06608814441179658</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-1.602580650042519</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.4951028059763534</v>
+        <v>0.4919019858187302</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.01760755327724783</v>
+        <v>0.01748841384980207</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-1.602580650042519</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.4636949268721994</v>
+        <v>0.4607066224258325</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.009781692697611824</v>
+        <v>0.009715655634874901</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52619,10 +52619,10 @@
         <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>1.204705233669806</v>
+        <v>1.157166170459627</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.4656342341753484</v>
+        <v>0.4626327737459778</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>0.02055262149565133</v>
+        <v>0.02041393983913546</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53414,10 +53414,10 @@
         <v>1</v>
       </c>
       <c r="JB66" t="n">
-        <v>1.204705233669806</v>
+        <v>1.157166170459627</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.4969713620693008</v>
+        <v>0.4937572820178666</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>0.008071650000553383</v>
+        <v>0.00801715168745923</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54209,10 +54209,10 @@
         <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>1.804705233669806</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.4925438210430937</v>
+        <v>0.4893599112037255</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>0.005747658675803096</v>
+        <v>0.00570798516769411</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-1.002580650042519</v>
+        <v>-1.045076465039656</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.4959629115345348</v>
+        <v>0.4927553872779843</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>0.002258604628475606</v>
+        <v>0.002243667825288305</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>1.804705233669806</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.4947293437335661</v>
+        <v>0.4915302914631194</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>0.001280538581285897</v>
+        <v>0.00127129010228384</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.602580650042519</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.4950291385650807</v>
+        <v>0.4918278935260622</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>0.000484711969194278</v>
+        <v>0.0004811888615022328</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.602580650042519</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.494716996237586</v>
+        <v>0.4915179608555997</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>0.0002239997722305638</v>
+        <v>0.0002228988117871476</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.602580650042519</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.494681037178661</v>
+        <v>0.4914822237819368</v>
       </c>
     </row>
     <row r="73">
@@ -58968,7 +58968,7 @@
         <v>0</v>
       </c>
       <c r="IY73" t="n">
-        <v>7.896183061281334e-05</v>
+        <v>7.815450531845937e-05</v>
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.602580650042519</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.4946144749816547</v>
+        <v>0.4914162507023255</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.602580650042519</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.4945747089354959</v>
+        <v>0.4913768153925931</v>
       </c>
     </row>
     <row r="75">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>1.204705233669806</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.4945696895748027</v>
+        <v>0.4913717960319002</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>1</v>
       </c>
       <c r="JB76" t="n">
-        <v>1.804705233669806</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.4945656715304591</v>
+        <v>0.4913677412390646</v>
       </c>
     </row>
     <row r="77">
@@ -62148,7 +62148,7 @@
         <v>0</v>
       </c>
       <c r="IY77" t="n">
-        <v>-1.195152058104458e-07</v>
+        <v>-8.167273192660964e-07</v>
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.002580650042519</v>
+        <v>-1.045076465039656</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.4945632368602683</v>
+        <v>0.4913651238356458</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.002580650042519</v>
+        <v>-1.045076465039656</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.4945577196182785</v>
+        <v>0.4913596065936561</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.602580650042519</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.4945513956242706</v>
+        <v>0.4913532825996482</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>1</v>
       </c>
       <c r="JB80" t="n">
-        <v>1.804705233669806</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.4945460278356923</v>
+        <v>0.4913479148110698</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>1.804705233669806</v>
+        <v>-1.045076465039656</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.494546064584184</v>
+        <v>0.4913479515595615</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>1</v>
       </c>
       <c r="JB82" t="n">
-        <v>1.804705233669806</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.4945461748296595</v>
+        <v>0.4913480618050371</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>1.804705233669806</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.4945462483266431</v>
+        <v>0.4913481353020207</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>1</v>
       </c>
       <c r="JB84" t="n">
-        <v>1.804705233669806</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.4945464320691023</v>
+        <v>0.4913483190444798</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>1</v>
       </c>
       <c r="JB85" t="n">
-        <v>1.804705233669806</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.4945479755057588</v>
+        <v>0.4913498624811363</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>1</v>
       </c>
       <c r="JB86" t="n">
-        <v>1.804705233669806</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.4945494454454318</v>
+        <v>0.4913513324208094</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>1</v>
       </c>
       <c r="JB87" t="n">
-        <v>1.804705233669806</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.4945506948941539</v>
+        <v>0.4913525818695314</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>1.804705233669806</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.4945520545883512</v>
+        <v>0.4913539415637287</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-1.602580650042519</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.4945498496788419</v>
+        <v>0.4913517366542194</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-1.602580650042519</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.4945494454454318</v>
+        <v>0.4913513324208094</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-1.602580650042519</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.4945486002301199</v>
+        <v>0.4913504872054975</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-1.602580650042519</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.4945491514574972</v>
+        <v>0.4913510384328747</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.602580650042519</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.4945488207210708</v>
+        <v>0.4913507076964483</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>1.204705233669806</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.4945485267331363</v>
+        <v>0.4913504137085138</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.602580650042519</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.4945486002301199</v>
+        <v>0.4913504872054975</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-1.002580650042519</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.4945481592482179</v>
+        <v>0.4913500462235955</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-1.602580650042519</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.4945480490027424</v>
+        <v>0.4913499359781199</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>1.804705233669806</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.4945480122542507</v>
+        <v>0.4913498992296282</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-1.002580650042519</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.4945481592482179</v>
+        <v>0.4913500462235955</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>1</v>
       </c>
       <c r="JB100" t="n">
-        <v>1.804705233669806</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.4945476815178243</v>
+        <v>0.4913495684932019</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>1</v>
       </c>
       <c r="JB101" t="n">
-        <v>1.804705233669806</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.4945486369786116</v>
+        <v>0.4913505239539891</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-1.002580650042519</v>
+        <v>-1.045076465039656</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.4945486002301199</v>
+        <v>0.4913504872054975</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-1.602580650042519</v>
+        <v>-1.045076465039656</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.4945482694936935</v>
+        <v>0.491350156469071</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-1.602580650042519</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.4945487104755955</v>
+        <v>0.491350597450973</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-1.602580650042519</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.4945480857512343</v>
+        <v>0.4913499727266119</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.602580650042519</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.4945479020087751</v>
+        <v>0.4913497889841527</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.602580650042519</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.4945474977753651</v>
+        <v>0.4913493847507427</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.602580650042519</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.4945466525600531</v>
+        <v>0.4913485395354307</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>1</v>
       </c>
       <c r="JB109" t="n">
-        <v>1.804705233669806</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.4945466158115615</v>
+        <v>0.491348502786939</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-1.002580650042519</v>
+        <v>-1.045076465039656</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.4945467628055287</v>
+        <v>0.4913486497809063</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>1</v>
       </c>
       <c r="JB111" t="n">
-        <v>1.804705233669806</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.4945466893085451</v>
+        <v>0.4913485762839226</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>1</v>
       </c>
       <c r="JB112" t="n">
-        <v>1.804705233669806</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.4945467628055287</v>
+        <v>0.4913486497809063</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-1.002580650042519</v>
+        <v>-1.045076465039656</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.4945467995540206</v>
+        <v>0.4913486865293982</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>1</v>
       </c>
       <c r="JB114" t="n">
-        <v>1.804705233669806</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.4945466893085451</v>
+        <v>0.4913485762839226</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-1.602580650042519</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.4945471302904471</v>
+        <v>0.4913490172658246</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>1</v>
       </c>
       <c r="JB116" t="n">
-        <v>1.804705233669806</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.4945470200449715</v>
+        <v>0.4913489070203491</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-1.602580650042519</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.4945469832964796</v>
+        <v>0.4913488702718571</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-1.602580650042519</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.4945469097994959</v>
+        <v>0.4913487967748735</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-1.602580650042519</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.4945468730510043</v>
+        <v>0.4913487600263818</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-1.602580650042519</v>
+        <v>-1.645076465039656</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.4945466525600531</v>
+        <v>0.4913485395354307</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB121" t="n">
-        <v>-1.602580650042519</v>
+        <v>1.157166170459627</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.4945465790630695</v>
+        <v>0.4913484660384471</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.602580650042519</v>
+        <v>-1.045076465039656</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.4945465055660859</v>
+        <v>0.4913483925414635</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-1.602580650042519</v>
+        <v>-1.045076465039656</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.4945465423145778</v>
+        <v>0.4913484292899554</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>1</v>
       </c>
       <c r="JB124" t="n">
-        <v>1.804705233669806</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.4945464320691023</v>
+        <v>0.4913483190444798</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>1</v>
       </c>
       <c r="JB125" t="n">
-        <v>1.804705233669806</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.4945465423145778</v>
+        <v>0.4913484292899554</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>1</v>
       </c>
       <c r="JB126" t="n">
-        <v>1.804705233669806</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.4945468363025123</v>
+        <v>0.4913487232778899</v>
       </c>
     </row>
   </sheetData>

--- a/out/MLP-mamba2_repeat_4_000008.xlsx
+++ b/out/MLP-mamba2_repeat_4_000008.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.602580650042519</v>
+        <v>0.02929985724364138</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>1.204705233669806</v>
+        <v>0.3501325296679072</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>1.804705233669806</v>
+        <v>0.5501325296679072</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-1.002580650042519</v>
+        <v>-0.09153281518062434</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.9331981600291558</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.2915328151806245</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>1</v>
       </c>
       <c r="JB8" t="n">
-        <v>1.204705233669806</v>
+        <v>-0.2915328151806243</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.2915328151806243</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.9331981600291558</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.2915328151806245</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>1</v>
       </c>
       <c r="JB12" t="n">
-        <v>1.204705233669806</v>
+        <v>-0.2915328151806243</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.002580650042519</v>
+        <v>0.5501325296679072</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12067,14 +12067,14 @@
       </c>
       <c r="IZ14" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA14" t="n">
         <v>1</v>
       </c>
       <c r="JB14" t="n">
-        <v>1.804705233669806</v>
+        <v>-0.09153281518062434</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-1.002580650042519</v>
+        <v>0.5501325296679072</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13657,14 +13657,14 @@
       </c>
       <c r="IZ16" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA16" t="n">
         <v>1</v>
       </c>
       <c r="JB16" t="n">
-        <v>1.804705233669806</v>
+        <v>-0.09153281518062434</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14452,14 +14452,14 @@
       </c>
       <c r="IZ17" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA17" t="n">
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.09153281518062434</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-1.002580650042519</v>
+        <v>-0.9331981600291558</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.9331981600291558</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.9331981600291558</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.9331981600291558</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.2915328151806245</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>1</v>
       </c>
       <c r="JB23" t="n">
-        <v>1.804705233669806</v>
+        <v>-0.2915328151806245</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-1.002580650042519</v>
+        <v>0.550132529667907</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA25" t="n">
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>1.804705233669806</v>
+        <v>-0.09153281518062445</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21607,14 +21607,14 @@
       </c>
       <c r="IZ26" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA26" t="n">
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-1.002580650042519</v>
+        <v>-0.09153281518062445</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-1.002580650042519</v>
+        <v>-0.7331981600291557</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.9331981600291558</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.2915328151806245</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>1</v>
       </c>
       <c r="JB30" t="n">
-        <v>1.804705233669806</v>
+        <v>0.550132529667907</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>1.804705233669806</v>
+        <v>1.191797874516439</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>1</v>
       </c>
       <c r="JB32" t="n">
-        <v>1.804705233669806</v>
+        <v>0.550132529667907</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-1.002580650042519</v>
+        <v>0.550132529667907</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>1</v>
       </c>
       <c r="JB34" t="n">
-        <v>1.804705233669806</v>
+        <v>0.550132529667907</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>1.804705233669806</v>
+        <v>0.550132529667907</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-1.002580650042519</v>
+        <v>0.550132529667907</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>1.804705233669806</v>
+        <v>-0.2915328151806245</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.2915328151806245</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.2915328151806245</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>1.204705233669806</v>
+        <v>0.350132529667907</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>1.804705233669806</v>
+        <v>1.191797874516439</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>1.804705233669806</v>
+        <v>1.191797874516439</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.804705233669806</v>
+        <v>1.191797874516439</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,7 +35924,7 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.804705233669806</v>
+        <v>1.191797874516439</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36719,10 +36719,10 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>1.804705233669806</v>
+        <v>0.550132529667907</v>
       </c>
       <c r="JC45" t="n">
-        <v>-0.0001411644149408676</v>
+        <v>-0.0001125482685550814</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.1621707996420336</v>
+        <v>-0.1292963436822218</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-1.602580650042519</v>
+        <v>0.550132529667907</v>
       </c>
       <c r="JC46" t="n">
-        <v>-0.1623119640569745</v>
+        <v>-0.1294088919507769</v>
       </c>
     </row>
     <row r="47">
@@ -38309,10 +38309,10 @@
         <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>1.204705233669806</v>
+        <v>-0.2915328151806245</v>
       </c>
       <c r="JC47" t="n">
-        <v>-0.1623119640569745</v>
+        <v>-0.1294088919507769</v>
       </c>
     </row>
     <row r="48">
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.2915328151806245</v>
       </c>
       <c r="JC48" t="n">
-        <v>-0.1623119640569745</v>
+        <v>-0.1294088919507769</v>
       </c>
     </row>
     <row r="49">
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.9331981600291558</v>
       </c>
       <c r="JC49" t="n">
-        <v>-0.1623119640569745</v>
+        <v>-0.1294088919507769</v>
       </c>
     </row>
     <row r="50">
@@ -40694,10 +40694,10 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.2915328151806245</v>
       </c>
       <c r="JC50" t="n">
-        <v>-0.1623119640569745</v>
+        <v>-0.1294088919507769</v>
       </c>
     </row>
     <row r="51">
@@ -41489,10 +41489,10 @@
         <v>1</v>
       </c>
       <c r="JB51" t="n">
-        <v>1.204705233669806</v>
+        <v>-0.2915328151806243</v>
       </c>
       <c r="JC51" t="n">
-        <v>-0.1623119640569745</v>
+        <v>-0.1294088919507769</v>
       </c>
     </row>
     <row r="52">
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.602580650042519</v>
+        <v>0.3501325296679071</v>
       </c>
       <c r="JC52" t="n">
-        <v>-0.1623119640569745</v>
+        <v>-0.1294088919507769</v>
       </c>
     </row>
     <row r="53">
@@ -43079,10 +43079,10 @@
         <v>1</v>
       </c>
       <c r="JB53" t="n">
-        <v>1.804705233669806</v>
+        <v>0.5501325296679072</v>
       </c>
       <c r="JC53" t="n">
-        <v>-0.1623119640569745</v>
+        <v>-0.1294088919507769</v>
       </c>
     </row>
     <row r="54">
@@ -43874,10 +43874,10 @@
         <v>1</v>
       </c>
       <c r="JB54" t="n">
-        <v>1.804705233669806</v>
+        <v>1.191797874516439</v>
       </c>
       <c r="JC54" t="n">
-        <v>-0.1623119640569745</v>
+        <v>-0.1294088919507769</v>
       </c>
     </row>
     <row r="55">
@@ -44669,10 +44669,10 @@
         <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>1.804705233669806</v>
+        <v>1.191797874516439</v>
       </c>
       <c r="JC55" t="n">
-        <v>-0.1623119640569745</v>
+        <v>-0.1294088919507769</v>
       </c>
     </row>
     <row r="56">
@@ -45464,10 +45464,10 @@
         <v>1</v>
       </c>
       <c r="JB56" t="n">
-        <v>1.804705233669806</v>
+        <v>1.191797874516439</v>
       </c>
       <c r="JC56" t="n">
-        <v>-0.1623119640569745</v>
+        <v>-0.1294088919507769</v>
       </c>
     </row>
     <row r="57">
@@ -46259,10 +46259,10 @@
         <v>1</v>
       </c>
       <c r="JB57" t="n">
-        <v>1.804705233669806</v>
+        <v>1.191797874516439</v>
       </c>
       <c r="JC57" t="n">
-        <v>-0.1623119640569745</v>
+        <v>-0.1294088919507769</v>
       </c>
     </row>
     <row r="58">
@@ -47054,10 +47054,10 @@
         <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>1.804705233669806</v>
+        <v>1.191797874516439</v>
       </c>
       <c r="JC58" t="n">
-        <v>-0.1623119640569745</v>
+        <v>-0.1294088919507769</v>
       </c>
     </row>
     <row r="59">
@@ -47849,10 +47849,10 @@
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>1.804705233669806</v>
+        <v>0.5501325296679072</v>
       </c>
       <c r="JC59" t="n">
-        <v>-0.1624338673807879</v>
+        <v>-0.1295080322865002</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.438336590095572</v>
+        <v>0.3564858122342162</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-1.602580650042519</v>
+        <v>0.3501325296679072</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.7150809351146759</v>
+        <v>0.5841485724743707</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.03123135342668109</v>
+        <v>0.02539957586164621</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>1</v>
       </c>
       <c r="JB61" t="n">
-        <v>1.204705233669806</v>
+        <v>0.3501325296679072</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.3385039852042352</v>
+        <v>0.277889555275552</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.05476915272888735</v>
+        <v>0.04454207356987269</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>1</v>
       </c>
       <c r="JB62" t="n">
-        <v>1.204705233669806</v>
+        <v>0.3501325296679072</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.416800698349921</v>
+        <v>0.3415659070647881</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.06653836416652441</v>
+        <v>0.05411367079678541</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.2915328151806243</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.4951028059763534</v>
+        <v>0.4052466802227637</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.01760755327724783</v>
+        <v>0.0143198331215284</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.2915328151806243</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.4636949268721994</v>
+        <v>0.3797035868393339</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.009781692697611824</v>
+        <v>0.007954300422652891</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52619,10 +52619,10 @@
         <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>1.204705233669806</v>
+        <v>0.3501325296679072</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.4656342341753484</v>
+        <v>0.3812798190211933</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>0.02055262149565133</v>
+        <v>0.01671422142475109</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53414,10 +53414,10 @@
         <v>1</v>
       </c>
       <c r="JB66" t="n">
-        <v>1.204705233669806</v>
+        <v>0.9917978745164386</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.4969713620693008</v>
+        <v>0.4067646559953636</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>0.008071650000553383</v>
+        <v>0.006563863338281834</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54209,10 +54209,10 @@
         <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>1.804705233669806</v>
+        <v>0.5501325296679072</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.4925438210430937</v>
+        <v>0.4031630045316103</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>0.005747658675803096</v>
+        <v>0.004673024086590104</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-1.002580650042519</v>
+        <v>0.5501325296679072</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.4959629115345348</v>
+        <v>0.4059424523315467</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>0.002258604628475606</v>
+        <v>0.001836300465634626</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55799,10 +55799,10 @@
         <v>1</v>
       </c>
       <c r="JB69" t="n">
-        <v>1.804705233669806</v>
+        <v>-0.2915328151806243</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.4947293437335661</v>
+        <v>0.404938388367201</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>0.001280538581285897</v>
+        <v>0.00104007812723242</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.2915328151806243</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.4950291385650807</v>
+        <v>0.4051811712158425</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>0.000484711969194278</v>
+        <v>0.0003931111692011037</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.9331981600291558</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.494716996237586</v>
+        <v>0.4049264799711884</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>0.0002239997722305638</v>
+        <v>0.0001810623149373331</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.9331981600291558</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.494681037178661</v>
+        <v>0.4048963119551274</v>
       </c>
     </row>
     <row r="73">
@@ -58968,7 +58968,7 @@
         <v>0</v>
       </c>
       <c r="IY73" t="n">
-        <v>7.896183061281334e-05</v>
+        <v>6.362265002008783e-05</v>
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.9331981600291558</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.4946144749816547</v>
+        <v>0.4048412369765593</v>
       </c>
     </row>
     <row r="74">
@@ -59763,7 +59763,7 @@
         <v>0</v>
       </c>
       <c r="IY74" t="n">
-        <v>1.980325908626812e-05</v>
+        <v>1.503340156967809e-05</v>
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.2915328151806242</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.4945747089354959</v>
+        <v>0.404808093105349</v>
       </c>
     </row>
     <row r="75">
@@ -60558,7 +60558,7 @@
         <v>0</v>
       </c>
       <c r="IY75" t="n">
-        <v>7.401629543134059e-06</v>
+        <v>5.016700784839047e-06</v>
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
@@ -60569,10 +60569,10 @@
         <v>1</v>
       </c>
       <c r="JB75" t="n">
-        <v>1.204705233669806</v>
+        <v>0.3501325296679072</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.4945696895748027</v>
+        <v>0.4048030774678663</v>
       </c>
     </row>
     <row r="76">
@@ -61353,7 +61353,7 @@
         <v>0</v>
       </c>
       <c r="IY76" t="n">
-        <v>1.677971888793091e-06</v>
+        <v>6.505915982095382e-07</v>
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
@@ -61364,10 +61364,10 @@
         <v>1</v>
       </c>
       <c r="JB76" t="n">
-        <v>1.804705233669806</v>
+        <v>0.5501325296679074</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.4945656715304591</v>
+        <v>0.4047988772585439</v>
       </c>
     </row>
     <row r="77">
@@ -62148,7 +62148,7 @@
         <v>0</v>
       </c>
       <c r="IY77" t="n">
-        <v>-1.195152058104458e-07</v>
+        <v>-1.513939432721747e-06</v>
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.002580650042519</v>
+        <v>-0.09153281518062417</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.4945632368602683</v>
+        <v>0.4047958933794382</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.002580650042519</v>
+        <v>-0.7331981600291557</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.4945577196182785</v>
+        <v>0.4047904496344318</v>
       </c>
     </row>
     <row r="79">
@@ -63738,7 +63738,7 @@
         <v>0</v>
       </c>
       <c r="IY79" t="n">
-        <v>-4.413072433009741e-06</v>
+        <v>-4.70653621650487e-06</v>
       </c>
       <c r="IZ79" t="inlineStr">
         <is>
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.2915328151806242</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.4945513956242706</v>
+        <v>0.4047844569010015</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>1</v>
       </c>
       <c r="JB80" t="n">
-        <v>1.804705233669806</v>
+        <v>0.5501325296679073</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.4945460278356923</v>
+        <v>0.4047790891124231</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>1</v>
       </c>
       <c r="JB81" t="n">
-        <v>1.804705233669806</v>
+        <v>1.191797874516439</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.494546064584184</v>
+        <v>0.4047791258609148</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>1</v>
       </c>
       <c r="JB82" t="n">
-        <v>1.804705233669806</v>
+        <v>1.191797874516439</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.4945461748296595</v>
+        <v>0.4047792361063904</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>1.804705233669806</v>
+        <v>1.191797874516439</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.4945462483266431</v>
+        <v>0.404779309603374</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>1</v>
       </c>
       <c r="JB84" t="n">
-        <v>1.804705233669806</v>
+        <v>1.191797874516439</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.4945464320691023</v>
+        <v>0.4047794933458331</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>1</v>
       </c>
       <c r="JB85" t="n">
-        <v>1.804705233669806</v>
+        <v>1.191797874516439</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.4945479755057588</v>
+        <v>0.4047810367824896</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>1</v>
       </c>
       <c r="JB86" t="n">
-        <v>1.804705233669806</v>
+        <v>1.191797874516439</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.4945494454454318</v>
+        <v>0.4047825067221627</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>1</v>
       </c>
       <c r="JB87" t="n">
-        <v>1.804705233669806</v>
+        <v>1.191797874516439</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.4945506948941539</v>
+        <v>0.4047837561708847</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>1.804705233669806</v>
+        <v>0.5501325296679074</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.4945520545883512</v>
+        <v>0.404785115865082</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.2915328151806242</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.4945498496788419</v>
+        <v>0.4047829109555727</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.9331981600291558</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.4945494454454318</v>
+        <v>0.4047825067221627</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.9331981600291558</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.4945486002301199</v>
+        <v>0.4047816615068507</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.9331981600291558</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.4945491514574972</v>
+        <v>0.404782212734228</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.2915328151806242</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.4945488207210708</v>
+        <v>0.4047818819978016</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>1</v>
       </c>
       <c r="JB94" t="n">
-        <v>1.204705233669806</v>
+        <v>-0.2915328151806242</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.4945485267331363</v>
+        <v>0.4047815880098671</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.2915328151806242</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.4945486002301199</v>
+        <v>0.4047816615068507</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-1.002580650042519</v>
+        <v>-0.9331981600291558</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.4945481592482179</v>
+        <v>0.4047812205249488</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.2915328151806242</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.4945480490027424</v>
+        <v>0.4047811102794732</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>1</v>
       </c>
       <c r="JB98" t="n">
-        <v>1.804705233669806</v>
+        <v>-0.09153281518062423</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.4945480122542507</v>
+        <v>0.4047810735309815</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-1.002580650042519</v>
+        <v>0.5501325296679073</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.4945481592482179</v>
+        <v>0.4047812205249488</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>1</v>
       </c>
       <c r="JB100" t="n">
-        <v>1.804705233669806</v>
+        <v>0.5501325296679073</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.4945476815178243</v>
+        <v>0.4047807427945552</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>1</v>
       </c>
       <c r="JB101" t="n">
-        <v>1.804705233669806</v>
+        <v>0.5501325296679074</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.4945486369786116</v>
+        <v>0.4047816982553424</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-1.002580650042519</v>
+        <v>-0.09153281518062417</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.4945486002301199</v>
+        <v>0.4047816615068507</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.9331981600291558</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.4945482694936935</v>
+        <v>0.4047813307704243</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.9331981600291558</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.4945487104755955</v>
+        <v>0.4047817717523263</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.9331981600291558</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.4945480857512343</v>
+        <v>0.4047811470279652</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.9331981600291558</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.4945479020087751</v>
+        <v>0.404780963285506</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.9331981600291558</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.4945474977753651</v>
+        <v>0.404780559052096</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.2915328151806242</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.4945466525600531</v>
+        <v>0.404779713836784</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>1</v>
       </c>
       <c r="JB109" t="n">
-        <v>1.804705233669806</v>
+        <v>-0.2915328151806242</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.4945466158115615</v>
+        <v>0.4047796770882923</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-1.002580650042519</v>
+        <v>0.5501325296679073</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.4945467628055287</v>
+        <v>0.4047798240822595</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>1</v>
       </c>
       <c r="JB111" t="n">
-        <v>1.804705233669806</v>
+        <v>0.5501325296679073</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.4945466893085451</v>
+        <v>0.4047797505852759</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>1</v>
       </c>
       <c r="JB112" t="n">
-        <v>1.804705233669806</v>
+        <v>0.5501325296679074</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.4945467628055287</v>
+        <v>0.4047798240822595</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-1.002580650042519</v>
+        <v>0.5501325296679074</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.4945467995540206</v>
+        <v>0.4047798608307515</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>1</v>
       </c>
       <c r="JB114" t="n">
-        <v>1.804705233669806</v>
+        <v>-0.09153281518062412</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.4945466893085451</v>
+        <v>0.4047797505852759</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-1.602580650042519</v>
+        <v>0.5501325296679074</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.4945471302904471</v>
+        <v>0.4047801915671779</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>1</v>
       </c>
       <c r="JB116" t="n">
-        <v>1.804705233669806</v>
+        <v>-0.2915328151806241</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.4945470200449715</v>
+        <v>0.4047800813217023</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.2915328151806241</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.4945469832964796</v>
+        <v>0.4047800445732104</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.9331981600291558</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.4945469097994959</v>
+        <v>0.4047799710762268</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.9331981600291558</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.4945468730510043</v>
+        <v>0.4047799343277351</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.9331981600291558</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.4945466525600531</v>
+        <v>0.404779713836784</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.9331981600291558</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.4945465790630695</v>
+        <v>0.4047796403398004</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.9331981600291558</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.4945465055660859</v>
+        <v>0.4047795668428168</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.2915328151806241</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.4945465423145778</v>
+        <v>0.4047796035913087</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>1</v>
       </c>
       <c r="JB124" t="n">
-        <v>1.804705233669806</v>
+        <v>0.5501325296679074</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.4945464320691023</v>
+        <v>0.4047794933458331</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>1</v>
       </c>
       <c r="JB125" t="n">
-        <v>1.804705233669806</v>
+        <v>1.191797874516439</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.4945465423145778</v>
+        <v>0.4047796035913087</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>1</v>
       </c>
       <c r="JB126" t="n">
-        <v>1.804705233669806</v>
+        <v>1.191797874516439</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.4945468363025123</v>
+        <v>0.4047798975792432</v>
       </c>
     </row>
   </sheetData>

--- a/out/MLP-mamba2_repeat_4_000008.xlsx
+++ b/out/MLP-mamba2_repeat_4_000008.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>0.4246917068958282</v>
       </c>
       <c r="JB2" t="n">
-        <v>0.02929985724364138</v>
+        <v>-0.1600000000000002</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="IZ3" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>1</v>
+        <v>0.899562656879425</v>
       </c>
       <c r="JB3" t="n">
-        <v>0.3501325296679072</v>
+        <v>-0.3000000000000002</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>1</v>
+        <v>0.9996827840805054</v>
       </c>
       <c r="JB4" t="n">
-        <v>0.5501325296679072</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0</v>
+        <v>0.2602292597293854</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.09153281518062434</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>0.01138276141136885</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.9331981600291558</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>0.1781059950590134</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.2915328151806245</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>1</v>
+        <v>0.6799079775810242</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.2915328151806243</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0</v>
+        <v>0.1072115451097488</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.2915328151806243</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>0.4659918248653412</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.9331981600291558</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0</v>
+        <v>0.1349689215421677</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.2915328151806245</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>1</v>
+        <v>0.8472461700439453</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.2915328151806243</v>
+        <v>0.3</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0</v>
+        <v>0.2872707545757294</v>
       </c>
       <c r="JB13" t="n">
-        <v>0.5501325296679072</v>
+        <v>0.16</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12067,14 +12067,14 @@
       </c>
       <c r="IZ14" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0.6960824728012085</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.09153281518062434</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0</v>
+        <v>0.4305577278137207</v>
       </c>
       <c r="JB15" t="n">
-        <v>0.5501325296679072</v>
+        <v>0.16</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13657,14 +13657,14 @@
       </c>
       <c r="IZ16" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>1</v>
+        <v>0.7825925350189209</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.09153281518062434</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14452,14 +14452,14 @@
       </c>
       <c r="IZ17" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0</v>
+        <v>0.0347667895257473</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.09153281518062434</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0</v>
+        <v>0.1655688285827637</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.9331981600291558</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0</v>
+        <v>0.1613335758447647</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.9331981600291558</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0</v>
+        <v>0.2694728672504425</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.9331981600291558</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0</v>
+        <v>0.403582751750946</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.9331981600291558</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0</v>
+        <v>0.133244201540947</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.2915328151806245</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0.5303650498390198</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.2915328151806245</v>
+        <v>0.3</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0</v>
+        <v>0.2653757035732269</v>
       </c>
       <c r="JB24" t="n">
-        <v>0.550132529667907</v>
+        <v>0.16</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0.7903506755828857</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.09153281518062445</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21607,14 +21607,14 @@
       </c>
       <c r="IZ26" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0</v>
+        <v>0.1051046401262283</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.09153281518062445</v>
+        <v>0.16</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0</v>
+        <v>0.4370872378349304</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.7331981600291557</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0</v>
+        <v>0.1867786347866058</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.9331981600291558</v>
+        <v>0.3</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0</v>
+        <v>0.4850859045982361</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.2915328151806245</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0.582004189491272</v>
       </c>
       <c r="JB30" t="n">
-        <v>0.550132529667907</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0.7028318643569946</v>
       </c>
       <c r="JB31" t="n">
-        <v>1.191797874516439</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0.9914631247520447</v>
       </c>
       <c r="JB32" t="n">
-        <v>0.550132529667907</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0</v>
+        <v>0.02318373695015907</v>
       </c>
       <c r="JB33" t="n">
-        <v>0.550132529667907</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0.6929223537445068</v>
       </c>
       <c r="JB34" t="n">
-        <v>0.550132529667907</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0.689259946346283</v>
       </c>
       <c r="JB35" t="n">
-        <v>0.550132529667907</v>
+        <v>0.3</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0</v>
+        <v>0.08690691739320755</v>
       </c>
       <c r="JB36" t="n">
-        <v>0.550132529667907</v>
+        <v>-0.3</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0.8813384175300598</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.2915328151806245</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0</v>
+        <v>0.1927356719970703</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.2915328151806245</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,10 +31946,10 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0</v>
+        <v>0.3885802328586578</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.2915328151806245</v>
+        <v>-0.3</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32741,10 +32741,10 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0.9236328601837158</v>
       </c>
       <c r="JB40" t="n">
-        <v>0.350132529667907</v>
+        <v>-0.16</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33536,10 +33536,10 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0.7566177845001221</v>
       </c>
       <c r="JB41" t="n">
-        <v>1.191797874516439</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0.9117193222045898</v>
       </c>
       <c r="JB42" t="n">
-        <v>1.191797874516439</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,10 +35126,10 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0.9480825662612915</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.191797874516439</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35921,10 +35921,10 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0.9990062117576599</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.191797874516439</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0.901680052280426</v>
       </c>
       <c r="JB45" t="n">
-        <v>0.550132529667907</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC45" t="n">
-        <v>-0.0001125482685550814</v>
+        <v>-0.0001132297395697096</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.1292963436822218</v>
+        <v>-0.1300792229893992</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0</v>
+        <v>0.0002539553388487548</v>
       </c>
       <c r="JB46" t="n">
-        <v>0.550132529667907</v>
+        <v>0.3</v>
       </c>
       <c r="JC46" t="n">
-        <v>-0.1294088919507769</v>
+        <v>-0.1301924527289689</v>
       </c>
     </row>
     <row r="47">
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>1</v>
+        <v>0.9595835208892822</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.2915328151806245</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC47" t="n">
-        <v>-0.1294088919507769</v>
+        <v>-0.1301924527289689</v>
       </c>
     </row>
     <row r="48">
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0</v>
+        <v>0.01421876810491085</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.2915328151806245</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC48" t="n">
-        <v>-0.1294088919507769</v>
+        <v>-0.1301924527289689</v>
       </c>
     </row>
     <row r="49">
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0</v>
+        <v>0.4813089072704315</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.9331981600291558</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC49" t="n">
-        <v>-0.1294088919507769</v>
+        <v>-0.1301924527289689</v>
       </c>
     </row>
     <row r="50">
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0</v>
+        <v>0.08705107867717743</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.2915328151806245</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC50" t="n">
-        <v>-0.1294088919507769</v>
+        <v>-0.1301924527289689</v>
       </c>
     </row>
     <row r="51">
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>1</v>
+        <v>0.7132503390312195</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.2915328151806243</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC51" t="n">
-        <v>-0.1294088919507769</v>
+        <v>-0.1301924527289689</v>
       </c>
     </row>
     <row r="52">
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0</v>
+        <v>0.1790265887975693</v>
       </c>
       <c r="JB52" t="n">
-        <v>0.3501325296679071</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC52" t="n">
-        <v>-0.1294088919507769</v>
+        <v>-0.1301924527289689</v>
       </c>
     </row>
     <row r="53">
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>1</v>
+        <v>0.9364579916000366</v>
       </c>
       <c r="JB53" t="n">
-        <v>0.5501325296679072</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC53" t="n">
-        <v>-0.1294088919507769</v>
+        <v>-0.1301924527289689</v>
       </c>
     </row>
     <row r="54">
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>1</v>
+        <v>0.5031176209449768</v>
       </c>
       <c r="JB54" t="n">
-        <v>1.191797874516439</v>
+        <v>0.3</v>
       </c>
       <c r="JC54" t="n">
-        <v>-0.1294088919507769</v>
+        <v>-0.1301924527289689</v>
       </c>
     </row>
     <row r="55">
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>1</v>
+        <v>0.7814675569534302</v>
       </c>
       <c r="JB55" t="n">
-        <v>1.191797874516439</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC55" t="n">
-        <v>-0.1294088919507769</v>
+        <v>-0.1301924527289689</v>
       </c>
     </row>
     <row r="56">
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>1</v>
+        <v>0.620928168296814</v>
       </c>
       <c r="JB56" t="n">
-        <v>1.191797874516439</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC56" t="n">
-        <v>-0.1294088919507769</v>
+        <v>-0.1301924527289689</v>
       </c>
     </row>
     <row r="57">
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>1</v>
+        <v>0.6649912595748901</v>
       </c>
       <c r="JB57" t="n">
-        <v>1.191797874516439</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC57" t="n">
-        <v>-0.1294088919507769</v>
+        <v>-0.1301924527289689</v>
       </c>
     </row>
     <row r="58">
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>0.9335379004478455</v>
       </c>
       <c r="JB58" t="n">
-        <v>1.191797874516439</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC58" t="n">
-        <v>-0.1294088919507769</v>
+        <v>-0.1301924527289689</v>
       </c>
     </row>
     <row r="59">
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0.9983000159263611</v>
       </c>
       <c r="JB59" t="n">
-        <v>0.5501325296679072</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC59" t="n">
-        <v>-0.1295080322865002</v>
+        <v>-0.1302921591422821</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.3564858122342162</v>
+        <v>0.3585212983285851</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0</v>
+        <v>0.00910017266869545</v>
       </c>
       <c r="JB60" t="n">
-        <v>0.3501325296679072</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.5841485724743707</v>
+        <v>0.5874393260151648</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.02539957586164621</v>
+        <v>0.02554460381850764</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>1</v>
+        <v>0.9478260278701782</v>
       </c>
       <c r="JB61" t="n">
-        <v>0.3501325296679072</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.277889555275552</v>
+        <v>0.2794316134925867</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.04454207356987269</v>
+        <v>0.04479640319212071</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>1</v>
+        <v>0.9923270344734192</v>
       </c>
       <c r="JB62" t="n">
-        <v>0.3501325296679072</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.3415659070647881</v>
+        <v>0.3434715481702604</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.05411367079678541</v>
+        <v>0.05442233946519297</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0</v>
+        <v>0.05053608119487762</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.2915328151806243</v>
+        <v>-0.1600000000000001</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.4052466802227637</v>
+        <v>0.4075159289919187</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.0143198331215284</v>
+        <v>0.01440167959800084</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0</v>
+        <v>0.2904853820800781</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.2915328151806243</v>
+        <v>-0.3</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.3797035868393339</v>
+        <v>0.3818268414356588</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.007954300422652891</v>
+        <v>0.007999792621427214</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0.9998119473457336</v>
       </c>
       <c r="JB65" t="n">
-        <v>0.3501325296679072</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.3812798190211933</v>
+        <v>0.3834121113124043</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>0.01671422142475109</v>
+        <v>0.01680975767701757</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0.7806050181388855</v>
       </c>
       <c r="JB66" t="n">
-        <v>0.9917978745164386</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.4067646559953636</v>
+        <v>0.4090426094816876</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>0.006563863338281834</v>
+        <v>0.006601406620635582</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0.966910719871521</v>
       </c>
       <c r="JB67" t="n">
-        <v>0.5501325296679072</v>
+        <v>-0.16</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.4031630045316103</v>
+        <v>0.4054204019347159</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>0.004673024086590104</v>
+        <v>0.004698898113617705</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0</v>
+        <v>0.03174110502004623</v>
       </c>
       <c r="JB68" t="n">
-        <v>0.5501325296679072</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.4059424523315467</v>
+        <v>0.408215764920396</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>0.001836300465634626</v>
+        <v>0.001847163595225391</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>1</v>
+        <v>0.8763185739517212</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.2915328151806243</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.404938388367201</v>
+        <v>0.4072058067733696</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>0.00104007812723242</v>
+        <v>0.001046243779900458</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>0.0298925694078207</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.2915328151806243</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.4051811712158425</v>
+        <v>0.407450051467726</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>0.0003931111692011037</v>
+        <v>0.0003954599076624671</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>0.07528800517320633</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.9331981600291558</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.4049264799711884</v>
+        <v>0.4071938871183836</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>0.0001810623149373331</v>
+        <v>0.0001821632753807493</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>0.01630916260182858</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.9331981600291558</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.4048963119551274</v>
+        <v>0.4071635706140441</v>
       </c>
     </row>
     <row r="73">
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>0.02145812660455704</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.9331981600291558</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.4048412369765593</v>
+        <v>0.4071082016475415</v>
       </c>
     </row>
     <row r="74">
@@ -59763,7 +59763,7 @@
         <v>0</v>
       </c>
       <c r="IY74" t="n">
-        <v>1.503340156967809e-05</v>
+        <v>1.551038732133709e-05</v>
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0</v>
+        <v>0.4542620182037354</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.2915328151806242</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.404808093105349</v>
+        <v>0.4070747262952626</v>
       </c>
     </row>
     <row r="75">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>1</v>
+        <v>0.5334624648094177</v>
       </c>
       <c r="JB75" t="n">
-        <v>0.3501325296679072</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.4048030774678663</v>
+        <v>0.4070697106577798</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>1</v>
+        <v>0.9297260642051697</v>
       </c>
       <c r="JB76" t="n">
-        <v>0.5501325296679074</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.4047988772585439</v>
+        <v>0.4070655104484575</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0</v>
+        <v>0.1973719894886017</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.09153281518062417</v>
+        <v>0.16</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.4047958933794382</v>
+        <v>0.4070625265693518</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0</v>
+        <v>0.01841331832110882</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.7331981600291557</v>
+        <v>0.16</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.4047904496344318</v>
+        <v>0.4070570828243454</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>0.1100962683558464</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.2915328151806242</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.4047844569010015</v>
+        <v>0.4070510900909151</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>1</v>
+        <v>0.5963844060897827</v>
       </c>
       <c r="JB80" t="n">
-        <v>0.5501325296679073</v>
+        <v>0.3</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.4047790891124231</v>
+        <v>0.4070457223023367</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>1</v>
+        <v>0.5906704068183899</v>
       </c>
       <c r="JB81" t="n">
-        <v>1.191797874516439</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.4047791258609148</v>
+        <v>0.4070457590508284</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>1</v>
+        <v>0.7893804311752319</v>
       </c>
       <c r="JB82" t="n">
-        <v>1.191797874516439</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.4047792361063904</v>
+        <v>0.4070458692963039</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>1</v>
+        <v>0.7158938050270081</v>
       </c>
       <c r="JB83" t="n">
-        <v>1.191797874516439</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.404779309603374</v>
+        <v>0.4070459427932876</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>1</v>
+        <v>0.9998668432235718</v>
       </c>
       <c r="JB84" t="n">
-        <v>1.191797874516439</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.4047794933458331</v>
+        <v>0.4070461265357467</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>1</v>
+        <v>0.9987401366233826</v>
       </c>
       <c r="JB85" t="n">
-        <v>1.191797874516439</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.4047810367824896</v>
+        <v>0.4070476699724032</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>1</v>
+        <v>0.9867860674858093</v>
       </c>
       <c r="JB86" t="n">
-        <v>1.191797874516439</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.4047825067221627</v>
+        <v>0.4070491399120763</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>1</v>
+        <v>0.9794996976852417</v>
       </c>
       <c r="JB87" t="n">
-        <v>1.191797874516439</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.4047837561708847</v>
+        <v>0.4070503893607983</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0.9517293572425842</v>
       </c>
       <c r="JB88" t="n">
-        <v>0.5501325296679074</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.404785115865082</v>
+        <v>0.4070517490549956</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0</v>
+        <v>0.006718650460243225</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.2915328151806242</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.4047829109555727</v>
+        <v>0.4070495441454863</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0</v>
+        <v>0.02934216894209385</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.9331981600291558</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.4047825067221627</v>
+        <v>0.4070491399120763</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0</v>
+        <v>0.2006650120019913</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.9331981600291558</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.4047816615068507</v>
+        <v>0.4070482946967643</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0</v>
+        <v>0.032799132168293</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.9331981600291558</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.404782212734228</v>
+        <v>0.4070488459241416</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0</v>
+        <v>0.03222223743796349</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.2915328151806242</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.4047818819978016</v>
+        <v>0.4070485151877152</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>1</v>
+        <v>0.5357009172439575</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.2915328151806242</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.4047815880098671</v>
+        <v>0.4070482211997807</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0</v>
+        <v>0.01013743411749601</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.2915328151806242</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.4047816615068507</v>
+        <v>0.4070482946967643</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0</v>
+        <v>0.3326743245124817</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.9331981600291558</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.4047812205249488</v>
+        <v>0.4070478537148624</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0</v>
+        <v>0.1698090881109238</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.2915328151806242</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.4047811102794732</v>
+        <v>0.4070477434693868</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>1</v>
+        <v>0.6213856339454651</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.09153281518062423</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.4047810735309815</v>
+        <v>0.4070477067208951</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0</v>
+        <v>0.009173166938126087</v>
       </c>
       <c r="JB99" t="n">
-        <v>0.5501325296679073</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.4047812205249488</v>
+        <v>0.4070478537148624</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>1</v>
+        <v>0.9986764788627625</v>
       </c>
       <c r="JB100" t="n">
-        <v>0.5501325296679073</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.4047807427945552</v>
+        <v>0.4070473759844687</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>1</v>
+        <v>0.8647003173828125</v>
       </c>
       <c r="JB101" t="n">
-        <v>0.5501325296679074</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.4047816982553424</v>
+        <v>0.407048331445256</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0</v>
+        <v>0.02157221548259258</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.09153281518062417</v>
+        <v>0.16</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.4047816615068507</v>
+        <v>0.4070482946967643</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0</v>
+        <v>0.2073665857315063</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.9331981600291558</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.4047813307704243</v>
+        <v>0.4070479639603379</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0</v>
+        <v>0.03562090173363686</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.9331981600291558</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.4047817717523263</v>
+        <v>0.4070484049422399</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0</v>
+        <v>0.0175451934337616</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.9331981600291558</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.4047811470279652</v>
+        <v>0.4070477802178787</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>0.05320878699421883</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.9331981600291558</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.404780963285506</v>
+        <v>0.4070475964754196</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0</v>
+        <v>0.002257103100419044</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.9331981600291558</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.404780559052096</v>
+        <v>0.4070471922420096</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0</v>
+        <v>0.09679663926362991</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.2915328151806242</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.404779713836784</v>
+        <v>0.4070463470266976</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>1</v>
+        <v>0.9291201829910278</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.2915328151806242</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.4047796770882923</v>
+        <v>0.4070463102782059</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0</v>
+        <v>0.2757533192634583</v>
       </c>
       <c r="JB110" t="n">
-        <v>0.5501325296679073</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.4047798240822595</v>
+        <v>0.4070464572721731</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>1</v>
+        <v>0.5944823026657104</v>
       </c>
       <c r="JB111" t="n">
-        <v>0.5501325296679073</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.4047797505852759</v>
+        <v>0.4070463837751895</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>1</v>
+        <v>0.9760977029800415</v>
       </c>
       <c r="JB112" t="n">
-        <v>0.5501325296679074</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.4047798240822595</v>
+        <v>0.4070464572721731</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0</v>
+        <v>0.03379495441913605</v>
       </c>
       <c r="JB113" t="n">
-        <v>0.5501325296679074</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.4047798608307515</v>
+        <v>0.4070464940206651</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0.9944077730178833</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.09153281518062412</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.4047797505852759</v>
+        <v>0.4070463837751895</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0</v>
+        <v>0.06309089809656143</v>
       </c>
       <c r="JB115" t="n">
-        <v>0.5501325296679074</v>
+        <v>0.16</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.4047801915671779</v>
+        <v>0.4070468247570915</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>1</v>
+        <v>0.6059213280677795</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.2915328151806241</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.4047800813217023</v>
+        <v>0.4070467145116159</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0</v>
+        <v>0.1625590473413467</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.2915328151806241</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.4047800445732104</v>
+        <v>0.407046677763124</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0</v>
+        <v>0.1815155148506165</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.9331981600291558</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.4047799710762268</v>
+        <v>0.4070466042661404</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0</v>
+        <v>0.07304520159959793</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.9331981600291558</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.4047799343277351</v>
+        <v>0.4070465675176487</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0</v>
+        <v>0.05919013544917107</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.9331981600291558</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.404779713836784</v>
+        <v>0.4070463470266976</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0</v>
+        <v>0.4768770039081573</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.9331981600291558</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.4047796403398004</v>
+        <v>0.407046273529714</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0</v>
+        <v>0.45004802942276</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.9331981600291558</v>
+        <v>0.3</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.4047795668428168</v>
+        <v>0.4070462000327303</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0</v>
+        <v>0.0778491199016571</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.2915328151806241</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.4047796035913087</v>
+        <v>0.4070462367812223</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>1</v>
+        <v>0.8918731212615967</v>
       </c>
       <c r="JB124" t="n">
-        <v>0.5501325296679074</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.4047794933458331</v>
+        <v>0.4070461265357467</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>1</v>
+        <v>0.9878597855567932</v>
       </c>
       <c r="JB125" t="n">
-        <v>1.191797874516439</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.4047796035913087</v>
+        <v>0.4070462367812223</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
+        <v>0.9029243588447571</v>
+      </c>
+      <c r="JB126" t="n">
         <v>1</v>
       </c>
-      <c r="JB126" t="n">
-        <v>1.191797874516439</v>
-      </c>
       <c r="JC126" t="n">
-        <v>0.4047798975792432</v>
+        <v>0.4070465307691568</v>
       </c>
     </row>
   </sheetData>

--- a/out/MLP-mamba2_repeat_4_000008.xlsx
+++ b/out/MLP-mamba2_repeat_4_000008.xlsx
@@ -2531,7 +2531,7 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0.4246917068958282</v>
+        <v>0.4246917366981506</v>
       </c>
       <c r="JB2" t="n">
         <v>-0.1600000000000002</v>
@@ -4916,7 +4916,7 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0.2602292597293854</v>
+        <v>0.2602292001247406</v>
       </c>
       <c r="JB5" t="n">
         <v>-0.4399999999999999</v>
@@ -6506,7 +6506,7 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0.1781059950590134</v>
+        <v>0.1781060397624969</v>
       </c>
       <c r="JB7" t="n">
         <v>-0.8599999999999999</v>
@@ -7301,7 +7301,7 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0.6799079775810242</v>
+        <v>0.6799080371856689</v>
       </c>
       <c r="JB8" t="n">
         <v>-0.7199999999999999</v>
@@ -8891,7 +8891,7 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0.4659918248653412</v>
+        <v>0.465991884469986</v>
       </c>
       <c r="JB10" t="n">
         <v>-0.4399999999999999</v>
@@ -13661,7 +13661,7 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0.7825925350189209</v>
+        <v>0.7825926542282104</v>
       </c>
       <c r="JB16" t="n">
         <v>0.1600000000000001</v>
@@ -15251,7 +15251,7 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0.1655688285827637</v>
+        <v>0.1655687987804413</v>
       </c>
       <c r="JB18" t="n">
         <v>-0.7199999999999999</v>
@@ -16046,7 +16046,7 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0.1613335758447647</v>
+        <v>0.1613335907459259</v>
       </c>
       <c r="JB19" t="n">
         <v>-0.8599999999999999</v>
@@ -18431,7 +18431,7 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0.133244201540947</v>
+        <v>0.1332441568374634</v>
       </c>
       <c r="JB22" t="n">
         <v>-0.5799999999999998</v>
@@ -19226,7 +19226,7 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0.5303650498390198</v>
+        <v>0.5303651690483093</v>
       </c>
       <c r="JB23" t="n">
         <v>0.3</v>
@@ -20816,7 +20816,7 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>0.7903506755828857</v>
+        <v>0.7903507351875305</v>
       </c>
       <c r="JB25" t="n">
         <v>0.4399999999999999</v>
@@ -22406,7 +22406,7 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0.4370872378349304</v>
+        <v>0.4370873868465424</v>
       </c>
       <c r="JB27" t="n">
         <v>0.4399999999999999</v>
@@ -23201,7 +23201,7 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0.1867786347866058</v>
+        <v>0.1867785453796387</v>
       </c>
       <c r="JB28" t="n">
         <v>0.3</v>
@@ -23996,7 +23996,7 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0.4850859045982361</v>
+        <v>0.4850860238075256</v>
       </c>
       <c r="JB29" t="n">
         <v>0.5799999999999998</v>
@@ -24791,7 +24791,7 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0.582004189491272</v>
+        <v>0.5820043683052063</v>
       </c>
       <c r="JB30" t="n">
         <v>0.5799999999999998</v>
@@ -25586,7 +25586,7 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0.7028318643569946</v>
+        <v>0.7028319239616394</v>
       </c>
       <c r="JB31" t="n">
         <v>0.5799999999999998</v>
@@ -28766,7 +28766,7 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0.689259946346283</v>
+        <v>0.6892600655555725</v>
       </c>
       <c r="JB35" t="n">
         <v>0.3</v>
@@ -29561,7 +29561,7 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0.08690691739320755</v>
+        <v>0.08690693229436874</v>
       </c>
       <c r="JB36" t="n">
         <v>-0.3</v>
@@ -31151,7 +31151,7 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0.1927356719970703</v>
+        <v>0.1927357017993927</v>
       </c>
       <c r="JB38" t="n">
         <v>-0.5799999999999998</v>
@@ -33536,7 +33536,7 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>0.7566177845001221</v>
+        <v>0.7566179037094116</v>
       </c>
       <c r="JB41" t="n">
         <v>0.7199999999999999</v>
@@ -36716,7 +36716,7 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>0.901680052280426</v>
+        <v>0.9016799330711365</v>
       </c>
       <c r="JB45" t="n">
         <v>0.5799999999999998</v>
@@ -37511,7 +37511,7 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0.0002539553388487548</v>
+        <v>0.0002539550769142807</v>
       </c>
       <c r="JB46" t="n">
         <v>0.3</v>
@@ -39101,7 +39101,7 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0.01421876810491085</v>
+        <v>0.01421875506639481</v>
       </c>
       <c r="JB48" t="n">
         <v>-0.7199999999999999</v>
@@ -42281,7 +42281,7 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0.1790265887975693</v>
+        <v>0.1790265738964081</v>
       </c>
       <c r="JB52" t="n">
         <v>-0.4399999999999999</v>
@@ -46256,7 +46256,7 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0.6649912595748901</v>
+        <v>0.6649913191795349</v>
       </c>
       <c r="JB57" t="n">
         <v>0.7199999999999999</v>
@@ -51026,7 +51026,7 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0.05053608119487762</v>
+        <v>0.05053612217307091</v>
       </c>
       <c r="JB63" t="n">
         <v>-0.1600000000000001</v>
@@ -51821,7 +51821,7 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0.2904853820800781</v>
+        <v>0.2904853224754333</v>
       </c>
       <c r="JB64" t="n">
         <v>-0.3</v>
@@ -55001,7 +55001,7 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0.03174110502004623</v>
+        <v>0.03174109011888504</v>
       </c>
       <c r="JB68" t="n">
         <v>-0.4399999999999999</v>
@@ -55796,7 +55796,7 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0.8763185739517212</v>
+        <v>0.8763185143470764</v>
       </c>
       <c r="JB69" t="n">
         <v>-0.5799999999999998</v>
@@ -56591,7 +56591,7 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0.0298925694078207</v>
+        <v>0.02989256381988525</v>
       </c>
       <c r="JB70" t="n">
         <v>-0.7199999999999999</v>
@@ -58976,7 +58976,7 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0.02145812660455704</v>
+        <v>0.02145813219249249</v>
       </c>
       <c r="JB73" t="n">
         <v>-0.7199999999999999</v>
@@ -65336,7 +65336,7 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0.5906704068183899</v>
+        <v>0.5906703472137451</v>
       </c>
       <c r="JB81" t="n">
         <v>0.5799999999999998</v>
@@ -66926,7 +66926,7 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0.7158938050270081</v>
+        <v>0.7158937454223633</v>
       </c>
       <c r="JB83" t="n">
         <v>0.8599999999999999</v>
@@ -71696,7 +71696,7 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0.006718650460243225</v>
+        <v>0.006718653719872236</v>
       </c>
       <c r="JB89" t="n">
         <v>-0.4399999999999999</v>
@@ -72491,7 +72491,7 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0.02934216894209385</v>
+        <v>0.02934222295880318</v>
       </c>
       <c r="JB90" t="n">
         <v>-0.7199999999999999</v>
@@ -74876,7 +74876,7 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0.03222223743796349</v>
+        <v>0.03222224488854408</v>
       </c>
       <c r="JB93" t="n">
         <v>-0.7199999999999999</v>
@@ -75671,7 +75671,7 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0.5357009172439575</v>
+        <v>0.5357006192207336</v>
       </c>
       <c r="JB94" t="n">
         <v>-0.7199999999999999</v>
@@ -76466,7 +76466,7 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0.01013743411749601</v>
+        <v>0.01013742946088314</v>
       </c>
       <c r="JB95" t="n">
         <v>-0.7199999999999999</v>
@@ -78056,7 +78056,7 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0.1698090881109238</v>
+        <v>0.1698091775178909</v>
       </c>
       <c r="JB97" t="n">
         <v>-0.1199999999999999</v>
@@ -78851,7 +78851,7 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0.6213856339454651</v>
+        <v>0.6213856935501099</v>
       </c>
       <c r="JB98" t="n">
         <v>0.1600000000000001</v>
@@ -79646,7 +79646,7 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0.009173166938126087</v>
+        <v>0.009173170663416386</v>
       </c>
       <c r="JB99" t="n">
         <v>0.4399999999999999</v>
@@ -82826,7 +82826,7 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0.2073665857315063</v>
+        <v>0.2073666304349899</v>
       </c>
       <c r="JB103" t="n">
         <v>-0.7199999999999999</v>
@@ -83621,7 +83621,7 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0.03562090173363686</v>
+        <v>0.03562092036008835</v>
       </c>
       <c r="JB104" t="n">
         <v>-0.9999999999999998</v>
@@ -85211,7 +85211,7 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0.05320878699421883</v>
+        <v>0.05320881307125092</v>
       </c>
       <c r="JB106" t="n">
         <v>-0.9999999999999998</v>
@@ -88391,7 +88391,7 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0.2757533192634583</v>
+        <v>0.2757533490657806</v>
       </c>
       <c r="JB110" t="n">
         <v>0.4399999999999999</v>
@@ -90776,7 +90776,7 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0.03379495441913605</v>
+        <v>0.03379496186971664</v>
       </c>
       <c r="JB113" t="n">
         <v>0.4399999999999999</v>
@@ -92366,7 +92366,7 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0.06309089809656143</v>
+        <v>0.06309088319540024</v>
       </c>
       <c r="JB115" t="n">
         <v>0.16</v>
@@ -93161,7 +93161,7 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0.6059213280677795</v>
+        <v>0.6059212684631348</v>
       </c>
       <c r="JB116" t="n">
         <v>0.1600000000000001</v>
@@ -93956,7 +93956,7 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0.1625590473413467</v>
+        <v>0.1625590324401855</v>
       </c>
       <c r="JB117" t="n">
         <v>-0.7199999999999999</v>
@@ -94751,7 +94751,7 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0.1815155148506165</v>
+        <v>0.1815154850482941</v>
       </c>
       <c r="JB118" t="n">
         <v>-0.7199999999999999</v>
@@ -97931,7 +97931,7 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0.45004802942276</v>
+        <v>0.4500480592250824</v>
       </c>
       <c r="JB122" t="n">
         <v>0.3</v>
@@ -99521,7 +99521,7 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0.8918731212615967</v>
+        <v>0.8918730020523071</v>
       </c>
       <c r="JB124" t="n">
         <v>0.7199999999999999</v>
